--- a/public/templates/Trips Import File.xlsx
+++ b/public/templates/Trips Import File.xlsx
@@ -1,42 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/150172908beba08a/Desktop/Basilmark Work Files/Gonyeti/Template Files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{74D4570E-0B32-4707-BACD-6A14726AD023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{998AE434-4029-45D8-AFFF-7227C1D98C30}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="1416" yWindow="996" windowWidth="21624" windowHeight="11244" xr2:uid="{7D19E1E8-97E3-4091-8E99-AFA43E61B6B0}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Trips" sheetId="1" r:id="rId1"/>
+    <sheet name="Trips" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>trip_type</t>
   </si>
@@ -68,24 +47,33 @@
     <t>cargo</t>
   </si>
   <si>
+    <t>loading_point</t>
+  </si>
+  <si>
     <t>offloading_point</t>
   </si>
   <si>
-    <t>loading_point</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
     <t>offloaded_weight</t>
   </si>
   <si>
+    <t>litreage_at_ambient</t>
+  </si>
+  <si>
+    <t>offloaded_litreage_at_ambient</t>
+  </si>
+  <si>
     <t>litreage_at_20</t>
   </si>
   <si>
     <t>offloaded_litreage_at_20</t>
   </si>
   <si>
+    <t>currency</t>
+  </si>
+  <si>
     <t>rate</t>
   </si>
   <si>
@@ -95,33 +83,114 @@
     <t>trip_status</t>
   </si>
   <si>
-    <t>currency</t>
-  </si>
-  <si>
-    <t>litreage_at_ambient</t>
-  </si>
-  <si>
-    <t>offloaded_litreage_at_ambient</t>
+    <t>cargo_type</t>
+  </si>
+  <si>
+    <t>cargo_details</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>freight_calculation_method</t>
+  </si>
+  <si>
+    <t>bill_of_entry</t>
+  </si>
+  <si>
+    <t>expenses</t>
+  </si>
+  <si>
+    <t>#Cross Border</t>
+  </si>
+  <si>
+    <t>REF-1001</t>
+  </si>
+  <si>
+    <t>Fast Haulage (Pvt) Ltd</t>
+  </si>
+  <si>
+    <t>ADK4533</t>
+  </si>
+  <si>
+    <t>AEZ4095, AEZ4096</t>
+  </si>
+  <si>
+    <t>Tatenda Chikwanha</t>
+  </si>
+  <si>
+    <t>Harare Fresh Produce (Pvt) Ltd</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>Mimosa Mine Loading Bay</t>
+  </si>
+  <si>
+    <t>Beira Port Terminal</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Offloaded</t>
+  </si>
+  <si>
+    <t>Solid</t>
+  </si>
+  <si>
+    <t>680 x 50kg bags</t>
+  </si>
+  <si>
+    <t>rate_weight</t>
+  </si>
+  <si>
+    <t>BOE-2026-0001</t>
+  </si>
+  <si>
+    <t>Tolls:120, Border Fees:85</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -134,8 +203,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF4D93D9"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,30 +220,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+  <cellXfs count="7">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="14" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="14" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -220,7 +280,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -272,7 +332,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -333,183 +393,210 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4650F2-A170-4724-A068-94AB9C60D2D0}">
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="4" width="18.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="15" width="18.109375" customWidth="1"/>
-    <col min="16" max="16" width="31.88671875" customWidth="1"/>
-    <col min="17" max="17" width="18.109375" customWidth="1"/>
-    <col min="18" max="19" width="24.21875" customWidth="1"/>
-    <col min="20" max="22" width="17.5546875" customWidth="1"/>
-    <col min="32" max="32" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="1"/>
+    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="1"/>
+    <col min="5" max="5" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="30.564" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="36.42" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="29" max="29" width="30.564" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="18.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -541,10 +628,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>12</v>
@@ -553,32 +640,144 @@
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>18</v>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5">
+        <v>46296.0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46299.0</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="6">
+        <v>34</v>
+      </c>
+      <c r="N2" s="6">
+        <v>33.8</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="6">
+        <v>45</v>
+      </c>
+      <c r="U2" s="6">
+        <v>1530</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>680</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>560</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/public/templates/Trips Import File.xlsx
+++ b/public/templates/Trips Import File.xlsx
@@ -1,21 +1,166 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gonyetitls\public\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5003C7-D973-4A8E-BDF6-D12391B9715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Trips" sheetId="1" r:id="rId4"/>
+    <sheet name="Trips" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>One or more loading points, separated by commas, in loading order. e.g. Mine A, Mine B</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>One or more offloading points, separated by commas, in drop order. e.g. Depot X, Depot Y</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Solid cargo. Loaded figure per loading point, comma-separated in the same order as loading_points (e.g. 20, 14). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Solid cargo. Offloaded figure per offloading point, comma-separated in the same order as offloading_points (e.g. 20000, 17950). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Liquid cargo, litres at ambient temperature. Loaded figure per loading point, comma-separated in the same order as loading_points (e.g. 20, 14). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Liquid cargo, litres at ambient temperature. Offloaded figure per offloading point, comma-separated in the same order as offloading_points (e.g. 20000, 17950). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Liquid cargo, litres corrected to 20°C. Loaded figure per loading point, comma-separated in the same order as loading_points (e.g. 20, 14). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Liquid cargo, litres corrected to 20°C. Offloaded figure per offloading point, comma-separated in the same order as offloading_points (e.g. 20000, 17950). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Solid cargo. Loaded figure per loading point, comma-separated in the same order as loading_points (e.g. 20, 14). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Solid cargo. Offloaded figure per offloading point, comma-separated in the same order as offloading_points (e.g. 20000, 17950). A single value is fine for one point. No thousand separators in lists.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>trip_type</t>
   </si>
@@ -47,10 +192,10 @@
     <t>cargo</t>
   </si>
   <si>
-    <t>loading_point</t>
-  </si>
-  <si>
-    <t>offloading_point</t>
+    <t>loading_points</t>
+  </si>
+  <si>
+    <t>offloading_points</t>
   </si>
   <si>
     <t>weight</t>
@@ -92,102 +237,137 @@
     <t>quantity</t>
   </si>
   <si>
+    <t>#Cross Border</t>
+  </si>
+  <si>
+    <t>REF-1001</t>
+  </si>
+  <si>
+    <t>Fast Haulage (Pvt) Ltd</t>
+  </si>
+  <si>
+    <t>ADK4533</t>
+  </si>
+  <si>
+    <t>AEZ4095, AEZ4096</t>
+  </si>
+  <si>
+    <t>Tatenda Chikwanha</t>
+  </si>
+  <si>
+    <t>Harare Fresh Produce (Pvt) Ltd</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>Mimosa Mine Loading Bay, Unki Mine Loading Bay</t>
+  </si>
+  <si>
+    <t>Beira Port Terminal</t>
+  </si>
+  <si>
+    <t>20, 14</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Offloaded</t>
+  </si>
+  <si>
+    <t>Solid</t>
+  </si>
+  <si>
+    <t>680 x 50kg bags</t>
+  </si>
+  <si>
+    <t>400, 280</t>
+  </si>
+  <si>
+    <t>Tolls:120, Border Fees:85</t>
+  </si>
+  <si>
+    <t>BOE-2026-0001</t>
+  </si>
+  <si>
+    <t>rate_weight</t>
+  </si>
+  <si>
+    <t>expenses</t>
+  </si>
+  <si>
+    <t>bill_of_entry</t>
+  </si>
+  <si>
+    <t>freight_calculation_method</t>
+  </si>
+  <si>
     <t>distance</t>
   </si>
   <si>
-    <t>freight_calculation_method</t>
-  </si>
-  <si>
-    <t>bill_of_entry</t>
-  </si>
-  <si>
-    <t>expenses</t>
-  </si>
-  <si>
-    <t>#Cross Border</t>
-  </si>
-  <si>
-    <t>REF-1001</t>
-  </si>
-  <si>
-    <t>Fast Haulage (Pvt) Ltd</t>
-  </si>
-  <si>
-    <t>ADK4533</t>
-  </si>
-  <si>
-    <t>AEZ4095, AEZ4096</t>
-  </si>
-  <si>
-    <t>Tatenda Chikwanha</t>
-  </si>
-  <si>
-    <t>Harare Fresh Produce (Pvt) Ltd</t>
-  </si>
-  <si>
-    <t>Maize</t>
-  </si>
-  <si>
-    <t>Mimosa Mine Loading Bay</t>
-  </si>
-  <si>
-    <t>Beira Port Terminal</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>Offloaded</t>
-  </si>
-  <si>
-    <t>Solid</t>
-  </si>
-  <si>
-    <t>680 x 50kg bags</t>
-  </si>
-  <si>
-    <t>rate_weight</t>
-  </si>
-  <si>
-    <t>BOE-2026-0001</t>
-  </si>
-  <si>
-    <t>Tolls:120, Border Fees:85</t>
+    <t>offloaded_quantity</t>
+  </si>
+  <si>
+    <t>#Local</t>
+  </si>
+  <si>
+    <t>REF-1002</t>
+  </si>
+  <si>
+    <t>ADK4534</t>
+  </si>
+  <si>
+    <t>AEZ4097</t>
+  </si>
+  <si>
+    <t>Farai Moyo</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Feruka Depot</t>
+  </si>
+  <si>
+    <t>Masvingo Service Station, Chivhu Service Station</t>
+  </si>
+  <si>
+    <t>20000, 17950</t>
+  </si>
+  <si>
+    <t>19820, 17790</t>
+  </si>
+  <si>
+    <t>Liquid</t>
+  </si>
+  <si>
+    <t>50ppm diesel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
@@ -221,19 +401,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="14" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="14" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -557,46 +745,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AD3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="1"/>
-    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="1"/>
-    <col min="5" max="5" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="36.42" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="18.33203125" customWidth="true" style="0"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" customWidth="1"/>
+    <col min="9" max="9" width="36.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="28.109375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" customWidth="1"/>
+    <col min="16" max="16" width="35.21875" customWidth="1"/>
+    <col min="17" max="17" width="17.5546875" customWidth="1"/>
+    <col min="18" max="18" width="29.44140625" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="12.88671875" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" customWidth="1"/>
+    <col min="25" max="27" width="10.5546875" customWidth="1"/>
+    <col min="28" max="28" width="31.6640625" customWidth="1"/>
+    <col min="29" max="29" width="16.44140625" customWidth="1"/>
+    <col min="30" max="30" width="30.5546875" customWidth="1"/>
+    <col min="33" max="33" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="2" customFormat="1">
+    <row r="1" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -673,67 +857,70 @@
         <v>24</v>
       </c>
       <c r="Z1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="C2" s="5">
+        <v>46296</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46299</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="5">
-        <v>46296.0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>46299.0</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="M2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="6">
-        <v>34</v>
-      </c>
       <c r="N2" s="6">
-        <v>33.8</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="T2" s="6">
         <v>45</v>
@@ -742,42 +929,116 @@
         <v>1530</v>
       </c>
       <c r="V2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Z2" s="6">
+        <v>680</v>
+      </c>
+      <c r="AA2" s="6">
+        <v>560</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>680</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>560</v>
-      </c>
-      <c r="AA2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46300</v>
+      </c>
+      <c r="D3" s="5">
+        <v>46301</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6">
+        <v>38000</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>37650</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="U3" s="6">
+        <v>1900</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6">
+        <v>290</v>
+      </c>
+      <c r="AB3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>